--- a/tabtools/demo/stratetab.xlsx
+++ b/tabtools/demo/stratetab.xlsx
@@ -100,953 +100,1007 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="225">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="238">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1074,7 +1128,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="162">
+  <borders count="175">
     <border>
       <left/>
       <right/>
@@ -2155,11 +2209,102 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -2775,6 +2920,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="224" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2848,7 +3045,7 @@
       <c r="G2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="108" t="s">
+      <c r="H2" s="162" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2874,7 +3071,7 @@
       <c r="G3" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="163" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2900,7 +3097,7 @@
       <c r="G4" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="122" t="s">
+      <c r="H4" s="164" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2926,7 +3123,7 @@
       <c r="G5" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="129" t="s">
+      <c r="H5" s="165" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2952,7 +3149,7 @@
       <c r="G6" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="136" t="s">
+      <c r="H6" s="166" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2960,25 +3157,25 @@
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="138" t="s">
+      <c r="C7" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="139" t="s">
+      <c r="D7" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="161" t="s">
+      <c r="E7" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="141" t="s">
+      <c r="F7" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="142" t="s">
+      <c r="G7" s="173" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="143" t="s">
+      <c r="H7" s="174" t="s">
         <v>26</v>
       </c>
     </row>

--- a/tabtools/demo/stratetab.xlsx
+++ b/tabtools/demo/stratetab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="27">
   <si>
     <t>Table 5. Incidence Rates by Drug Class</t>
   </si>
@@ -100,10 +100,2038 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="238">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="712">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1128,7 +3156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="175">
+  <borders count="523">
     <border>
       <left/>
       <right/>
@@ -2300,11 +4328,2339 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="523">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -2975,6 +7331,1344 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" xfId="0"/>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" xfId="0"/>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="690" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="698" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="706" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2987,195 +8681,195 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="4" customWidth="true"/>
-    <col min="4" max="4" width="17.7109375" style="5" customWidth="true"/>
-    <col min="5" max="5" width="20.7109375" style="6" customWidth="true"/>
-    <col min="6" max="6" width="7.7109375" style="7" customWidth="true"/>
-    <col min="7" max="7" width="17.7109375" style="8" customWidth="true"/>
-    <col min="8" max="8" width="20.7109375" style="9" customWidth="true"/>
+    <col min="1" max="1" width="5.7109375" style="350" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="351" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="352" customWidth="true"/>
+    <col min="4" max="4" width="17.7109375" style="353" customWidth="true"/>
+    <col min="5" max="5" width="20.7109375" style="354" customWidth="true"/>
+    <col min="6" max="6" width="7.7109375" style="355" customWidth="true"/>
+    <col min="7" max="7" width="17.7109375" style="356" customWidth="true"/>
+    <col min="8" max="8" width="20.7109375" style="357" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="349" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="390" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="390" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="390" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="498" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="451" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="452" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="156" t="s">
+      <c r="E2" s="504" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="106" t="s">
+      <c r="F2" s="454" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="G2" s="455" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="162" t="s">
+      <c r="H2" s="510" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="499" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="458" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="459" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="157" t="s">
+      <c r="E3" s="505" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="113" t="s">
+      <c r="F3" s="461" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="114" t="s">
+      <c r="G3" s="462" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="163" t="s">
+      <c r="H3" s="511" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="500" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="465" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="466" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="506" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="120" t="s">
+      <c r="F4" s="468" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="121" t="s">
+      <c r="G4" s="469" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="164" t="s">
+      <c r="H4" s="512" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="153" t="s">
+      <c r="B5" s="501" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="124" t="s">
+      <c r="C5" s="472" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="125" t="s">
+      <c r="D5" s="473" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="159" t="s">
+      <c r="E5" s="507" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="127" t="s">
+      <c r="F5" s="475" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="128" t="s">
+      <c r="G5" s="476" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="513" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="502" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="131" t="s">
+      <c r="C6" s="479" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="132" t="s">
+      <c r="D6" s="480" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="160" t="s">
+      <c r="E6" s="508" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="134" t="s">
+      <c r="F6" s="482" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="135" t="s">
+      <c r="G6" s="483" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="166" t="s">
+      <c r="H6" s="514" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="516" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="169" t="s">
+      <c r="C7" s="517" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="170" t="s">
+      <c r="D7" s="518" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="171" t="s">
+      <c r="E7" s="519" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="172" t="s">
+      <c r="F7" s="520" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="173" t="s">
+      <c r="G7" s="521" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="174" t="s">
+      <c r="H7" s="522" t="s">
         <v>26</v>
       </c>
     </row>

--- a/tabtools/demo/stratetab.xlsx
+++ b/tabtools/demo/stratetab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="224" uniqueCount="27">
   <si>
     <t>Table 5. Incidence Rates by Drug Class</t>
   </si>
@@ -100,10 +100,1024 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="712">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="949">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3156,7 +4170,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="523">
+  <borders count="697">
     <border>
       <left/>
       <right/>
@@ -6656,11 +7670,1175 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="523">
+  <cellXfs count="697">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -8669,6 +10847,675 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="523" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="524" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="525" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="526" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="527" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="528" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="529" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="530" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="531" xfId="0"/>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8681,195 +11528,195 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="350" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="351" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="352" customWidth="true"/>
-    <col min="4" max="4" width="17.7109375" style="353" customWidth="true"/>
-    <col min="5" max="5" width="20.7109375" style="354" customWidth="true"/>
-    <col min="6" max="6" width="7.7109375" style="355" customWidth="true"/>
-    <col min="7" max="7" width="17.7109375" style="356" customWidth="true"/>
-    <col min="8" max="8" width="20.7109375" style="357" customWidth="true"/>
+    <col min="1" max="1" width="5.7109375" style="524" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="525" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="526" customWidth="true"/>
+    <col min="4" max="4" width="17.7109375" style="527" customWidth="true"/>
+    <col min="5" max="5" width="20.7109375" style="528" customWidth="true"/>
+    <col min="6" max="6" width="7.7109375" style="529" customWidth="true"/>
+    <col min="7" max="7" width="17.7109375" style="530" customWidth="true"/>
+    <col min="8" max="8" width="20.7109375" style="531" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="349" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="390" t="s">
+    <row r="1" s="523" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="564" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="390" t="s">
+      <c r="B1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="390" t="s">
+      <c r="C1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="390" t="s">
+      <c r="D1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="390" t="s">
+      <c r="E1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="390" t="s">
+      <c r="F1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="390" t="s">
+      <c r="G1" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="390" t="s">
+      <c r="H1" s="564" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="176" t="s">
+      <c r="A2" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="498" t="s">
+      <c r="B2" s="672" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="451" t="s">
+      <c r="C2" s="625" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="452" t="s">
+      <c r="D2" s="626" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="504" t="s">
+      <c r="E2" s="678" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="454" t="s">
+      <c r="F2" s="628" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="455" t="s">
+      <c r="G2" s="629" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="510" t="s">
+      <c r="H2" s="684" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="499" t="s">
+      <c r="B3" s="673" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="458" t="s">
+      <c r="C3" s="632" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="459" t="s">
+      <c r="D3" s="633" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="505" t="s">
+      <c r="E3" s="679" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="461" t="s">
+      <c r="F3" s="635" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="462" t="s">
+      <c r="G3" s="636" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="511" t="s">
+      <c r="H3" s="685" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="500" t="s">
+      <c r="B4" s="674" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="465" t="s">
+      <c r="C4" s="639" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="466" t="s">
+      <c r="D4" s="640" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="506" t="s">
+      <c r="E4" s="680" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="468" t="s">
+      <c r="F4" s="642" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="469" t="s">
+      <c r="G4" s="643" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="512" t="s">
+      <c r="H4" s="686" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="501" t="s">
+      <c r="B5" s="675" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="472" t="s">
+      <c r="C5" s="646" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="473" t="s">
+      <c r="D5" s="647" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="507" t="s">
+      <c r="E5" s="681" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="475" t="s">
+      <c r="F5" s="649" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="476" t="s">
+      <c r="G5" s="650" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="513" t="s">
+      <c r="H5" s="687" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="176" t="s">
+      <c r="A6" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="502" t="s">
+      <c r="B6" s="676" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="479" t="s">
+      <c r="C6" s="653" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="480" t="s">
+      <c r="D6" s="654" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="508" t="s">
+      <c r="E6" s="682" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="482" t="s">
+      <c r="F6" s="656" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="483" t="s">
+      <c r="G6" s="657" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="514" t="s">
+      <c r="H6" s="688" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="176" t="s">
+      <c r="A7" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="516" t="s">
+      <c r="B7" s="690" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="517" t="s">
+      <c r="C7" s="691" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="518" t="s">
+      <c r="D7" s="692" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="519" t="s">
+      <c r="E7" s="693" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="520" t="s">
+      <c r="F7" s="694" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="521" t="s">
+      <c r="G7" s="695" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="522" t="s">
+      <c r="H7" s="696" t="s">
         <v>26</v>
       </c>
     </row>

--- a/tabtools/demo/stratetab.xlsx
+++ b/tabtools/demo/stratetab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="224" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="27">
   <si>
     <t>Table 5. Incidence Rates by Drug Class</t>
   </si>
@@ -100,10 +100,1024 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="949">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1186">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4170,7 +5184,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="697">
+  <borders count="871">
     <border>
       <left/>
       <right/>
@@ -8834,11 +9848,1175 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="697">
+  <cellXfs count="871">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -11516,6 +13694,675 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="697" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="698" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="699" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="700" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="701" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="702" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="703" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="704" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="705" xfId="0"/>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1155" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1157" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1158" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1159" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1160" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1161" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1162" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1163" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1164" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1165" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1166" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1167" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1168" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1169" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1170" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1171" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1172" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1173" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1174" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1175" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1176" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1177" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1178" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1179" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1180" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1181" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1182" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1183" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1184" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1185" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11528,195 +14375,195 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="524" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="525" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="526" customWidth="true"/>
-    <col min="4" max="4" width="17.7109375" style="527" customWidth="true"/>
-    <col min="5" max="5" width="20.7109375" style="528" customWidth="true"/>
-    <col min="6" max="6" width="7.7109375" style="529" customWidth="true"/>
-    <col min="7" max="7" width="17.7109375" style="530" customWidth="true"/>
-    <col min="8" max="8" width="20.7109375" style="531" customWidth="true"/>
+    <col min="1" max="1" width="5.7109375" style="698" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="699" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="700" customWidth="true"/>
+    <col min="4" max="4" width="17.7109375" style="701" customWidth="true"/>
+    <col min="5" max="5" width="20.7109375" style="702" customWidth="true"/>
+    <col min="6" max="6" width="7.7109375" style="703" customWidth="true"/>
+    <col min="7" max="7" width="17.7109375" style="704" customWidth="true"/>
+    <col min="8" max="8" width="20.7109375" style="705" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="523" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="564" t="s">
+    <row r="1" s="697" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="738" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="564" t="s">
+      <c r="B1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="564" t="s">
+      <c r="C1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="564" t="s">
+      <c r="D1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="564" t="s">
+      <c r="E1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="564" t="s">
+      <c r="F1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="564" t="s">
+      <c r="G1" s="738" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="564" t="s">
+      <c r="H1" s="738" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="672" t="s">
+      <c r="B2" s="846" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="625" t="s">
+      <c r="C2" s="799" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="626" t="s">
+      <c r="D2" s="800" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="678" t="s">
+      <c r="E2" s="852" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="628" t="s">
+      <c r="F2" s="802" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="629" t="s">
+      <c r="G2" s="803" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="684" t="s">
+      <c r="H2" s="858" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="350" t="s">
+      <c r="A3" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="673" t="s">
+      <c r="B3" s="847" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="632" t="s">
+      <c r="C3" s="806" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="633" t="s">
+      <c r="D3" s="807" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="679" t="s">
+      <c r="E3" s="853" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="635" t="s">
+      <c r="F3" s="809" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="636" t="s">
+      <c r="G3" s="810" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="685" t="s">
+      <c r="H3" s="859" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="674" t="s">
+      <c r="B4" s="848" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="639" t="s">
+      <c r="C4" s="813" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="640" t="s">
+      <c r="D4" s="814" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="680" t="s">
+      <c r="E4" s="854" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="642" t="s">
+      <c r="F4" s="816" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="643" t="s">
+      <c r="G4" s="817" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="686" t="s">
+      <c r="H4" s="860" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="350" t="s">
+      <c r="A5" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="675" t="s">
+      <c r="B5" s="849" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="646" t="s">
+      <c r="C5" s="820" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="647" t="s">
+      <c r="D5" s="821" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="681" t="s">
+      <c r="E5" s="855" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="649" t="s">
+      <c r="F5" s="823" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="650" t="s">
+      <c r="G5" s="824" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="687" t="s">
+      <c r="H5" s="861" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="350" t="s">
+      <c r="A6" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="676" t="s">
+      <c r="B6" s="850" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="653" t="s">
+      <c r="C6" s="827" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="654" t="s">
+      <c r="D6" s="828" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="682" t="s">
+      <c r="E6" s="856" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="656" t="s">
+      <c r="F6" s="830" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="657" t="s">
+      <c r="G6" s="831" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="688" t="s">
+      <c r="H6" s="862" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="350" t="s">
+      <c r="A7" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="690" t="s">
+      <c r="B7" s="864" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="691" t="s">
+      <c r="C7" s="865" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="692" t="s">
+      <c r="D7" s="866" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="693" t="s">
+      <c r="E7" s="867" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="694" t="s">
+      <c r="F7" s="868" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="695" t="s">
+      <c r="G7" s="869" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="696" t="s">
+      <c r="H7" s="870" t="s">
         <v>26</v>
       </c>
     </row>
